--- a/experiment/HAT+CNN_2CH_bestx4/Test/results_table_HAT+CNN_2CH.xlsx
+++ b/experiment/HAT+CNN_2CH_bestx4/Test/results_table_HAT+CNN_2CH.xlsx
@@ -570,37 +570,37 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>32.262/
-0.8942</t>
+          <t>32.278/
+0.8943</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>28.643/
+          <t>28.659/
 0.7831</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>27.602/
+          <t>27.609/
 0.7382</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>26.079/
-0.7867</t>
+          <t>26.082/
+0.7864</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>30.541/
-0.9097</t>
+          <t>30.589/
+0.9100</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>29.025/
+          <t>29.043/
 0.8224</t>
         </is>
       </c>
